--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -617,10 +617,10 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2">
         <v>47</v>
@@ -629,10 +629,10 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M2" s="1">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -711,10 +711,10 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M4" s="1">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -731,7 +731,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -740,10 +740,10 @@
         <v>28</v>
       </c>
       <c r="H5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J5">
         <v>236</v>
@@ -766,10 +766,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -781,10 +781,10 @@
         <v>23</v>
       </c>
       <c r="H6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>24</v>
@@ -793,7 +793,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M6" s="1">
         <v>95.3</v>
@@ -848,13 +848,13 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -875,10 +875,10 @@
         <v>35</v>
       </c>
       <c r="L8">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M8" s="1">
-        <v>70.3</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -889,13 +889,13 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>32</v>
@@ -904,10 +904,10 @@
         <v>35</v>
       </c>
       <c r="H9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9">
         <v>115</v>
@@ -916,10 +916,10 @@
         <v>89</v>
       </c>
       <c r="L9">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M9" s="1">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -927,13 +927,13 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F10">
         <v>47</v>
@@ -954,10 +954,10 @@
         <v>291</v>
       </c>
       <c r="L10">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="M10" s="1">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1022,10 +1022,10 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M2" s="1">
         <v>100</v>
@@ -1104,13 +1104,13 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D4">
         <v>56</v>
       </c>
       <c r="E4">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M4" s="1">
         <v>100</v>
@@ -1148,10 +1148,10 @@
         <v>603</v>
       </c>
       <c r="D5">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E5">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1186,10 +1186,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D6">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M6" s="1">
         <v>100</v>
@@ -1268,13 +1268,13 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>28</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M8" s="1">
         <v>100</v>
@@ -1309,13 +1309,13 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D9">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E9">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="M9" s="1">
         <v>100</v>
@@ -1347,13 +1347,13 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="D10">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E10">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="M10" s="1">
         <v>100</v>
@@ -1442,7 +1442,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -1457,10 +1457,10 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2">
         <v>47</v>
@@ -1469,10 +1469,10 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M2" s="1">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1524,13 +1524,13 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1551,10 +1551,10 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M4" s="1">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1571,7 +1571,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -1580,10 +1580,10 @@
         <v>28</v>
       </c>
       <c r="H5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J5">
         <v>236</v>
@@ -1606,10 +1606,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -1621,10 +1621,10 @@
         <v>23</v>
       </c>
       <c r="H6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>24</v>
@@ -1633,7 +1633,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M6" s="1">
         <v>95.3</v>
@@ -1688,13 +1688,13 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -1715,10 +1715,10 @@
         <v>35</v>
       </c>
       <c r="L8">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M8" s="1">
-        <v>70.3</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1729,13 +1729,13 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>32</v>
@@ -1744,10 +1744,10 @@
         <v>35</v>
       </c>
       <c r="H9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9">
         <v>115</v>
@@ -1756,10 +1756,10 @@
         <v>89</v>
       </c>
       <c r="L9">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M9" s="1">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1767,13 +1767,13 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F10">
         <v>47</v>
@@ -1794,10 +1794,10 @@
         <v>291</v>
       </c>
       <c r="L10">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="M10" s="1">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1932,7 +1932,7 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1950,7 +1950,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -1959,10 +1959,10 @@
         <v>14</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" s="1">
-        <v>58.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1970,7 +1970,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -1997,10 +1997,10 @@
         <v>17</v>
       </c>
       <c r="K5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" s="1">
-        <v>56.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2426,13 +2426,13 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L17" s="1">
         <v>100</v>
@@ -2578,7 +2578,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         <v>4</v>
       </c>
       <c r="H21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L21" s="1">
         <v>100</v>
@@ -2616,7 +2616,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -2631,7 +2631,7 @@
         <v>6</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22">
         <v>8</v>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L22" s="1">
         <v>100</v>
@@ -2692,10 +2692,10 @@
         <v>39</v>
       </c>
       <c r="B24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L24" s="1">
         <v>100</v>
@@ -3072,13 +3072,13 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3099,10 +3099,10 @@
         <v>2</v>
       </c>
       <c r="K34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L34" s="1">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
     </row>
   </sheetData>
@@ -3201,7 +3201,7 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>14</v>
@@ -3213,13 +3213,13 @@
         <v>14</v>
       </c>
       <c r="F4" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3227,7 +3227,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>17</v>
@@ -3239,13 +3239,13 @@
         <v>17</v>
       </c>
       <c r="F5" s="1">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3539,7 +3539,7 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3669,7 +3669,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>39</v>
       </c>
       <c r="B24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3981,7 +3981,7 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -3993,13 +3993,13 @@
         <v>2</v>
       </c>
       <c r="F34" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
     </row>
   </sheetData>

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -611,28 +611,28 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L2">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="M2" s="1">
-        <v>69.2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -643,7 +643,7 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -655,25 +655,25 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K3">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="M3" s="1">
-        <v>45.2</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -684,7 +684,7 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -696,25 +696,25 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="K4">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="L4">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="M4" s="1">
-        <v>88.8</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -725,7 +725,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -734,28 +734,28 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J5">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="K5">
-        <v>202</v>
+        <v>347</v>
       </c>
       <c r="L5">
-        <v>401</v>
+        <v>257</v>
       </c>
       <c r="M5" s="1">
-        <v>66.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -766,37 +766,37 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G6">
+        <v>21</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6">
         <v>23</v>
       </c>
-      <c r="H6">
-        <v>28</v>
-      </c>
-      <c r="I6">
-        <v>36</v>
-      </c>
       <c r="J6">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="L6">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M6" s="1">
-        <v>95.3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -807,7 +807,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -816,28 +816,28 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J7">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="L7">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1">
-        <v>69.09999999999999</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -854,31 +854,31 @@
         <v>0</v>
       </c>
       <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
       <c r="H8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="J8">
         <v>30</v>
       </c>
       <c r="K8">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="L8">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="M8" s="1">
-        <v>69.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -892,34 +892,34 @@
         <v>434</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="J9">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="K9">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="L9">
-        <v>345</v>
+        <v>241</v>
       </c>
       <c r="M9" s="1">
-        <v>79.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -927,37 +927,37 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G10">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I10">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="J10">
-        <v>351</v>
+        <v>198</v>
       </c>
       <c r="K10">
-        <v>291</v>
+        <v>540</v>
       </c>
       <c r="L10">
-        <v>746</v>
+        <v>498</v>
       </c>
       <c r="M10" s="1">
-        <v>71.90000000000001</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1022,34 +1022,34 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D2">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M2" s="1">
         <v>100</v>
@@ -1063,37 +1063,37 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>218</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>221</v>
       </c>
       <c r="M3" s="1">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1104,37 +1104,37 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D4">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>187</v>
       </c>
       <c r="M4" s="1">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1145,37 +1145,37 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D5">
-        <v>251</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>348</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M5" s="1">
-        <v>100</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1186,34 +1186,34 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D6">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M6" s="1">
         <v>100</v>
@@ -1227,37 +1227,37 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L7">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="M7" s="1">
-        <v>100</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1271,34 +1271,34 @@
         <v>116</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="M8" s="1">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1312,34 +1312,34 @@
         <v>434</v>
       </c>
       <c r="D9">
-        <v>197</v>
+        <v>18</v>
       </c>
       <c r="E9">
-        <v>226</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L9">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="M9" s="1">
-        <v>100</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1347,37 +1347,37 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D10">
-        <v>448</v>
+        <v>35</v>
       </c>
       <c r="E10">
-        <v>574</v>
+        <v>50</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>300</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L10">
-        <v>1037</v>
+        <v>981</v>
       </c>
       <c r="M10" s="1">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
   </sheetData>
@@ -1442,37 +1442,37 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>25</v>
+      </c>
+      <c r="I2">
         <v>13</v>
       </c>
-      <c r="G2">
-        <v>14</v>
-      </c>
-      <c r="H2">
-        <v>26</v>
-      </c>
-      <c r="I2">
-        <v>26</v>
-      </c>
       <c r="J2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="L2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="M2" s="1">
-        <v>69.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1483,37 +1483,37 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K3">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="M3" s="1">
-        <v>45.2</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1524,37 +1524,37 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="K4">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="L4">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="M4" s="1">
-        <v>88.8</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1565,37 +1565,37 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D5">
         <v>6</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="J5">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="K5">
-        <v>202</v>
+        <v>383</v>
       </c>
       <c r="L5">
-        <v>401</v>
+        <v>221</v>
       </c>
       <c r="M5" s="1">
-        <v>66.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1606,37 +1606,37 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
         <v>15</v>
       </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
       <c r="G6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H6">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J6">
         <v>24</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="L6">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="M6" s="1">
-        <v>95.3</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1647,7 +1647,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1659,25 +1659,25 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>7</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="L7">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="M7" s="1">
-        <v>69.09999999999999</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1694,31 +1694,31 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>4</v>
       </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
       <c r="I8">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="L8">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="M8" s="1">
-        <v>69.8</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1732,34 +1732,34 @@
         <v>434</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>31</v>
+      </c>
+      <c r="H9">
         <v>32</v>
       </c>
-      <c r="G9">
-        <v>35</v>
-      </c>
-      <c r="H9">
-        <v>43</v>
-      </c>
       <c r="I9">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="J9">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="K9">
-        <v>89</v>
+        <v>190</v>
       </c>
       <c r="L9">
-        <v>345</v>
+        <v>244</v>
       </c>
       <c r="M9" s="1">
-        <v>79.5</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1767,37 +1767,37 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="G10">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="H10">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I10">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="J10">
-        <v>351</v>
+        <v>184</v>
       </c>
       <c r="K10">
-        <v>291</v>
+        <v>573</v>
       </c>
       <c r="L10">
-        <v>746</v>
+        <v>465</v>
       </c>
       <c r="M10" s="1">
-        <v>71.90000000000001</v>
+        <v>44.8</v>
       </c>
     </row>
   </sheetData>
@@ -1868,25 +1868,25 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="1">
-        <v>66.7</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1903,19 +1903,19 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -1932,37 +1932,37 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
       <c r="J4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L4" s="1">
-        <v>60</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1976,31 +1976,31 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K5">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L5" s="1">
-        <v>57.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2017,28 +2017,28 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>12</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L6" s="1">
-        <v>69.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2049,34 +2049,34 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L7" s="1">
-        <v>100</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2099,22 +2099,22 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="L8" s="1">
-        <v>100</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2128,31 +2128,31 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L9" s="1">
-        <v>26.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2172,25 +2172,25 @@
         <v>0</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
         <v>4</v>
       </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>5</v>
-      </c>
       <c r="J10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2210,25 +2210,25 @@
         <v>0</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+      <c r="I11">
         <v>4</v>
       </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
       <c r="J11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L11" s="1">
-        <v>38.6</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2248,25 +2248,25 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>3</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K12">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L12" s="1">
-        <v>62.5</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2274,7 +2274,7 @@
         <v>28</v>
       </c>
       <c r="B13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -2298,13 +2298,13 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13" s="1">
-        <v>27</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2324,16 +2324,16 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
         <v>4</v>
-      </c>
-      <c r="I14">
-        <v>3</v>
       </c>
       <c r="J14">
         <v>20</v>
@@ -2368,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K15">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="L15" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2400,25 +2400,25 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K16">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L16" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2444,19 +2444,19 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K17">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="L17" s="1">
-        <v>100</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2467,34 +2467,34 @@
         <v>28</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
         <v>5</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>17</v>
       </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
       <c r="K18">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="L18" s="1">
-        <v>96.40000000000001</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2502,7 +2502,7 @@
         <v>34</v>
       </c>
       <c r="B19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2520,19 +2520,19 @@
         <v>2</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K19">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="L19" s="1">
-        <v>100</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2543,34 +2543,34 @@
         <v>36</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
         <v>4</v>
       </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
       <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20">
         <v>4</v>
       </c>
-      <c r="G20">
+      <c r="H20">
+        <v>6</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
         <v>7</v>
       </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-      <c r="I20">
-        <v>6</v>
-      </c>
-      <c r="J20">
-        <v>8</v>
-      </c>
       <c r="K20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L20" s="1">
-        <v>77.8</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2578,37 +2578,37 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L21" s="1">
-        <v>100</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2622,10 +2622,10 @@
         <v>2</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22">
         <v>6</v>
@@ -2634,19 +2634,19 @@
         <v>4</v>
       </c>
       <c r="H22">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K22">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L22" s="1">
-        <v>100</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2657,34 +2657,34 @@
         <v>37</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>8</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H23">
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23">
         <v>4</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
       <c r="K23">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L23" s="1">
-        <v>100</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2695,34 +2695,34 @@
         <v>19</v>
       </c>
       <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
         <v>3</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
         <v>7</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
       <c r="K24">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L24" s="1">
-        <v>100</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2739,28 +2739,28 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
         <v>3</v>
       </c>
-      <c r="G25">
-        <v>3</v>
-      </c>
-      <c r="H25">
-        <v>6</v>
-      </c>
       <c r="I25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L25" s="1">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2768,7 +2768,7 @@
         <v>41</v>
       </c>
       <c r="B26">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2777,28 +2777,28 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
         <v>3</v>
       </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26">
-        <v>8</v>
-      </c>
       <c r="I26">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K26">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="L26" s="1">
-        <v>90.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2824,19 +2824,19 @@
         <v>1</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27">
         <v>2</v>
       </c>
       <c r="J27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L27" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2859,22 +2859,22 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K28">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L28" s="1">
-        <v>100</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2926,31 +2926,31 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K30">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L30" s="1">
-        <v>100</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2970,16 +2970,16 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J31">
         <v>14</v>
@@ -3014,19 +3014,19 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L32" s="1">
-        <v>100</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -3046,25 +3046,25 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L33" s="1">
-        <v>26.9</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3087,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>4</v>
       </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
       <c r="I34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L34" s="1">
-        <v>83.3</v>
+        <v>41.7</v>
       </c>
     </row>
   </sheetData>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <v>33.3</v>
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>33.3</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3201,7 +3201,7 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>14</v>
@@ -3210,16 +3210,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>40</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1">
         <v>42.5</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>42.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1">
         <v>30.8</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>30.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3282,22 +3282,22 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3308,22 +3308,22 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3334,22 +3334,22 @@
         <v>42</v>
       </c>
       <c r="C9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1">
-        <v>73.8</v>
+        <v>76.2</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>73.8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1">
         <v>66.7</v>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3389,19 +3389,19 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1">
         <v>61.4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H11" s="1">
-        <v>61.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1">
         <v>37.5</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>37.5</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3435,25 +3435,25 @@
         <v>28</v>
       </c>
       <c r="B13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1">
-        <v>73</v>
+        <v>73.7</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>73</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3490,22 +3490,22 @@
         <v>38</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3516,22 +3516,22 @@
         <v>25</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3542,22 +3542,22 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3568,22 +3568,22 @@
         <v>28</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1">
+        <v>60.7</v>
+      </c>
+      <c r="G18" s="1">
         <v>3.6</v>
       </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
       <c r="H18" s="1">
-        <v>3.6</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3591,25 +3591,25 @@
         <v>34</v>
       </c>
       <c r="B19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>63.9</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1">
         <v>22.2</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3643,25 +3643,25 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3672,22 +3672,22 @@
         <v>39</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3698,22 +3698,22 @@
         <v>37</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3724,22 +3724,22 @@
         <v>19</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3750,22 +3750,22 @@
         <v>25</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3773,25 +3773,25 @@
         <v>41</v>
       </c>
       <c r="B26">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F26" s="1">
-        <v>9.5</v>
+        <v>63.4</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>31.7</v>
       </c>
       <c r="H26" s="1">
-        <v>9.5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" s="1">
         <v>64</v>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3828,22 +3828,22 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3880,22 +3880,22 @@
         <v>28</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3932,22 +3932,22 @@
         <v>17</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3961,19 +3961,19 @@
         <v>19</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1">
         <v>73.09999999999999</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>53.8</v>
       </c>
       <c r="H33" s="1">
-        <v>73.09999999999999</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F34" s="1">
         <v>16.7</v>
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>16.7</v>
+        <v>58.3</v>
       </c>
     </row>
   </sheetData>

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -702,10 +702,10 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K4">
         <v>137</v>
@@ -743,10 +743,10 @@
         <v>45</v>
       </c>
       <c r="I5">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K5">
         <v>347</v>
@@ -945,10 +945,10 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K10">
         <v>540</v>
@@ -1025,34 +1025,34 @@
         <v>194</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G2">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <v>31</v>
+      </c>
+      <c r="J2">
+        <v>71</v>
+      </c>
+      <c r="K2">
         <v>30</v>
       </c>
-      <c r="H2">
-        <v>37</v>
-      </c>
-      <c r="I2">
-        <v>49</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="M2" s="1">
-        <v>100</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1075,25 +1075,25 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="J3">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="L3">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="M3" s="1">
-        <v>99.5</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1116,25 +1116,25 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="L4">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="M4" s="1">
-        <v>99.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1148,34 +1148,34 @@
         <v>604</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H5">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>210</v>
+        <v>59</v>
       </c>
       <c r="J5">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>234</v>
       </c>
       <c r="L5">
-        <v>602</v>
+        <v>370</v>
       </c>
       <c r="M5" s="1">
-        <v>99.7</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1192,31 +1192,31 @@
         <v>17</v>
       </c>
       <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6">
+        <v>27</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
         <v>21</v>
       </c>
-      <c r="F6">
-        <v>38</v>
-      </c>
-      <c r="G6">
-        <v>55</v>
-      </c>
-      <c r="H6">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L6">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="M6" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1239,25 +1239,25 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="K7">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="L7">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="M7" s="1">
-        <v>72.3</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1271,34 +1271,34 @@
         <v>116</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="I8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="M8" s="1">
-        <v>87.90000000000001</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1312,34 +1312,34 @@
         <v>434</v>
       </c>
       <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
         <v>18</v>
       </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
       <c r="F9">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G9">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="I9">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="J9">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="K9">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="L9">
-        <v>379</v>
+        <v>280</v>
       </c>
       <c r="M9" s="1">
-        <v>87.3</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1350,34 +1350,34 @@
         <v>1038</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="G10">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="H10">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="I10">
-        <v>300</v>
+        <v>112</v>
       </c>
       <c r="J10">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="K10">
-        <v>57</v>
+        <v>388</v>
       </c>
       <c r="L10">
-        <v>981</v>
+        <v>650</v>
       </c>
       <c r="M10" s="1">
-        <v>94.5</v>
+        <v>62.6</v>
       </c>
     </row>
   </sheetData>
@@ -1448,22 +1448,22 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K2">
         <v>85</v>
@@ -1492,28 +1492,28 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3">
         <v>30</v>
       </c>
       <c r="K3">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M3" s="1">
-        <v>27.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1533,28 +1533,28 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K4">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L4">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M4" s="1">
-        <v>27.1</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1571,31 +1571,31 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L5">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M5" s="1">
-        <v>36.6</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1609,34 +1609,34 @@
         <v>170</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
         <v>21</v>
       </c>
-      <c r="I6">
-        <v>26</v>
-      </c>
       <c r="J6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M6" s="1">
-        <v>79.40000000000001</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1656,10 +1656,10 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -1668,16 +1668,16 @@
         <v>12</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M7" s="1">
-        <v>35.1</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1703,22 +1703,22 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L8">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M8" s="1">
-        <v>49.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1732,25 +1732,25 @@
         <v>434</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>31</v>
       </c>
       <c r="H9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J9">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K9">
         <v>190</v>
@@ -1770,34 +1770,34 @@
         <v>1038</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E10">
         <v>26</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H10">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I10">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J10">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="K10">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="L10">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="M10" s="1">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
     </row>
   </sheetData>
@@ -1859,19 +1859,19 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
         <v>3</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1897,22 +1897,22 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>6</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -2017,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -2052,22 +2052,22 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
         <v>6</v>
       </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -2172,16 +2172,16 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>27</v>
@@ -2213,13 +2213,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H11">
         <v>7</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>28</v>
@@ -2283,28 +2283,28 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1">
-        <v>26.3</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2397,28 +2397,28 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2447,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L17" s="1">
-        <v>25.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2482,10 +2482,10 @@
         <v>3</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18">
         <v>17</v>
@@ -2520,19 +2520,19 @@
         <v>2</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19">
         <v>8</v>
       </c>
       <c r="J19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L19" s="1">
-        <v>36.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2546,22 +2546,22 @@
         <v>4</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20">
         <v>4</v>
-      </c>
-      <c r="F20">
-        <v>7</v>
       </c>
       <c r="G20">
         <v>4</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2581,34 +2581,34 @@
         <v>39</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21">
         <v>5</v>
       </c>
-      <c r="G21">
-        <v>6</v>
-      </c>
       <c r="H21">
+        <v>5</v>
+      </c>
+      <c r="I21">
         <v>8</v>
       </c>
-      <c r="I21">
-        <v>11</v>
-      </c>
       <c r="J21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L21" s="1">
-        <v>87.2</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2619,10 +2619,10 @@
         <v>39</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -2631,22 +2631,22 @@
         <v>6</v>
       </c>
       <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
         <v>4</v>
       </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
       <c r="I22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L22" s="1">
-        <v>69.2</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2657,34 +2657,34 @@
         <v>37</v>
       </c>
       <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23">
         <v>3</v>
-      </c>
-      <c r="D23">
-        <v>4</v>
       </c>
       <c r="E23">
         <v>4</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
         <v>4</v>
       </c>
-      <c r="H23">
-        <v>5</v>
-      </c>
       <c r="I23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L23" s="1">
-        <v>89.2</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2695,7 +2695,7 @@
         <v>19</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -2704,25 +2704,25 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L24" s="1">
-        <v>63.2</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2815,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2827,16 +2827,16 @@
         <v>3</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L27" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2938,19 +2938,19 @@
         <v>1</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L30" s="1">
-        <v>42.9</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2973,22 +2973,22 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K31">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L31" s="1">
-        <v>57.6</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3087,10 +3087,10 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -3155,7 +3155,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -3164,7 +3164,7 @@
         <v>33.3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="H2" s="1">
         <v>29.6</v>
@@ -3233,7 +3233,7 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>22</v>
@@ -3242,7 +3242,7 @@
         <v>42.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H5" s="1">
         <v>55</v>
@@ -3363,7 +3363,7 @@
         <v>24</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E10">
         <v>27</v>
@@ -3372,7 +3372,7 @@
         <v>66.7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H10" s="1">
         <v>75</v>
@@ -3389,7 +3389,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E11">
         <v>28</v>
@@ -3398,7 +3398,7 @@
         <v>61.4</v>
       </c>
       <c r="G11" s="1">
-        <v>2.3</v>
+        <v>63.6</v>
       </c>
       <c r="H11" s="1">
         <v>63.6</v>
@@ -3441,19 +3441,19 @@
         <v>28</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1">
         <v>73.7</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>76.3</v>
       </c>
       <c r="H13" s="1">
-        <v>73.7</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3493,7 +3493,7 @@
         <v>34</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E15">
         <v>34</v>
@@ -3502,7 +3502,7 @@
         <v>89.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H15" s="1">
         <v>89.5</v>
@@ -3519,19 +3519,19 @@
         <v>20</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="1">
         <v>80</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H16" s="1">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3545,19 +3545,19 @@
         <v>23</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1">
         <v>74.2</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>74.2</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3571,7 +3571,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -3580,7 +3580,7 @@
         <v>60.7</v>
       </c>
       <c r="G18" s="1">
-        <v>3.6</v>
+        <v>60.7</v>
       </c>
       <c r="H18" s="1">
         <v>60.7</v>
@@ -3597,19 +3597,19 @@
         <v>23</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1">
         <v>63.9</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H19" s="1">
-        <v>63.9</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3623,7 +3623,7 @@
         <v>8</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>7</v>
@@ -3632,7 +3632,7 @@
         <v>22.2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="H20" s="1">
         <v>19.4</v>
@@ -3649,19 +3649,19 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1">
         <v>15.4</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="H21" s="1">
-        <v>12.8</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3675,19 +3675,19 @@
         <v>11</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F22" s="1">
         <v>28.2</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="H22" s="1">
-        <v>30.8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3701,19 +3701,19 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" s="1">
         <v>5.4</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="H23" s="1">
-        <v>10.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3727,19 +3727,19 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1">
         <v>36.8</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>31.6</v>
       </c>
       <c r="H24" s="1">
-        <v>36.8</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" s="1">
         <v>64</v>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3857,7 +3857,7 @@
         <v>26</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E29">
         <v>26</v>
@@ -3866,7 +3866,7 @@
         <v>86.7</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H29" s="1">
         <v>86.7</v>
@@ -3883,19 +3883,19 @@
         <v>18</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1">
         <v>64.3</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>60.7</v>
       </c>
       <c r="H30" s="1">
-        <v>57.1</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3909,19 +3909,19 @@
         <v>14</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1">
         <v>42.4</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="H31" s="1">
-        <v>42.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3987,7 +3987,7 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -3996,7 +3996,7 @@
         <v>16.7</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="H34" s="1">
         <v>58.3</v>

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -1031,28 +1031,28 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H2">
+        <v>16</v>
+      </c>
+      <c r="I2">
         <v>17</v>
       </c>
-      <c r="I2">
-        <v>31</v>
-      </c>
       <c r="J2">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="L2">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="M2" s="1">
-        <v>84.5</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1075,25 +1075,25 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="L3">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="M3" s="1">
-        <v>62.2</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1154,28 +1154,28 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J5">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="K5">
-        <v>234</v>
+        <v>361</v>
       </c>
       <c r="L5">
-        <v>370</v>
+        <v>243</v>
       </c>
       <c r="M5" s="1">
-        <v>61.3</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1236,28 +1236,28 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>14</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="L7">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="M7" s="1">
-        <v>54.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1283,22 +1283,22 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J8">
         <v>29</v>
       </c>
       <c r="K8">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L8">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="M8" s="1">
-        <v>54.3</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1318,28 +1318,28 @@
         <v>18</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I9">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J9">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="K9">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="L9">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="M9" s="1">
-        <v>64.5</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1356,28 +1356,28 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G10">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="I10">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J10">
-        <v>316</v>
+        <v>205</v>
       </c>
       <c r="K10">
-        <v>388</v>
+        <v>538</v>
       </c>
       <c r="L10">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="M10" s="1">
-        <v>62.6</v>
+        <v>48.2</v>
       </c>
     </row>
   </sheetData>
@@ -1454,13 +1454,13 @@
         <v>6</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>21</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2">
         <v>43</v>
@@ -1504,16 +1504,16 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M3" s="1">
-        <v>27</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1577,25 +1577,25 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5">
         <v>36</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K5">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L5">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M5" s="1">
-        <v>35.9</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1656,10 +1656,10 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -1700,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>14</v>
@@ -1738,13 +1738,13 @@
         <v>17</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9">
         <v>47</v>
@@ -1776,28 +1776,28 @@
         <v>26</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K10">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L10">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M10" s="1">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
     </row>
   </sheetData>
@@ -1947,10 +1947,10 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -2058,10 +2058,10 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -2257,16 +2257,16 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1">
-        <v>34.4</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2815,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2970,10 +2970,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>3</v>
@@ -3207,7 +3207,7 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>21</v>
@@ -3216,7 +3216,7 @@
         <v>41.2</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>61.8</v>
       </c>
       <c r="H4" s="1">
         <v>61.8</v>
@@ -3259,7 +3259,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -3268,7 +3268,7 @@
         <v>30.8</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="H6" s="1">
         <v>46.2</v>
@@ -3285,7 +3285,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -3294,7 +3294,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H7" s="1">
         <v>26.7</v>
@@ -3311,7 +3311,7 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>23</v>
@@ -3320,7 +3320,7 @@
         <v>70</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="H8" s="1">
         <v>76.7</v>
@@ -3337,7 +3337,7 @@
         <v>32</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E9">
         <v>34</v>
@@ -3346,7 +3346,7 @@
         <v>76.2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H9" s="1">
         <v>81</v>
@@ -3415,19 +3415,19 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1">
         <v>37.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>65.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3805,7 +3805,7 @@
         <v>16</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>16</v>
@@ -3814,7 +3814,7 @@
         <v>64</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H27" s="1">
         <v>64</v>
@@ -3935,7 +3935,7 @@
         <v>8</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -3944,7 +3944,7 @@
         <v>47.1</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>41.2</v>
       </c>
       <c r="H32" s="1">
         <v>47.1</v>

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -1028,31 +1028,31 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>7</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="L2">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="M2" s="1">
-        <v>60.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1151,31 +1151,31 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>10</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J5">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K5">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="L5">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M5" s="1">
-        <v>40.2</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1236,28 +1236,28 @@
         <v>4</v>
       </c>
       <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
         <v>3</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
       </c>
       <c r="H7">
         <v>8</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K7">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="L7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="M7" s="1">
-        <v>43.9</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1318,28 +1318,28 @@
         <v>18</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9">
         <v>33</v>
       </c>
       <c r="I9">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J9">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K9">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L9">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="M9" s="1">
-        <v>59.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1353,31 +1353,31 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I10">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J10">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="K10">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="L10">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="M10" s="1">
-        <v>48.2</v>
+        <v>46.4</v>
       </c>
     </row>
   </sheetData>
@@ -1451,10 +1451,10 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>21</v>
@@ -1574,10 +1574,10 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5">
         <v>36</v>
@@ -1653,31 +1653,31 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
         <v>3</v>
       </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
       <c r="H7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M7" s="1">
-        <v>35.8</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1709,16 +1709,16 @@
         <v>14</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M8" s="1">
-        <v>47.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1735,31 +1735,31 @@
         <v>17</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9">
         <v>22</v>
       </c>
       <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
         <v>33</v>
       </c>
-      <c r="H9">
-        <v>32</v>
-      </c>
       <c r="I9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J9">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K9">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L9">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M9" s="1">
-        <v>56.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1773,31 +1773,31 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K10">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="L10">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M10" s="1">
-        <v>44.2</v>
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
@@ -1903,10 +1903,10 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -2774,31 +2774,31 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K26">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L26" s="1">
-        <v>39</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -3017,16 +3017,16 @@
         <v>3</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L32" s="1">
-        <v>52.9</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -3190,7 +3190,7 @@
         <v>33.3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H3" s="1">
         <v>33.3</v>
@@ -3779,19 +3779,19 @@
         <v>26</v>
       </c>
       <c r="D26">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F26" s="1">
         <v>63.4</v>
       </c>
       <c r="G26" s="1">
-        <v>31.7</v>
+        <v>56.1</v>
       </c>
       <c r="H26" s="1">
-        <v>61</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3938,7 +3938,7 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" s="1">
         <v>47.1</v>
@@ -3947,7 +3947,7 @@
         <v>41.2</v>
       </c>
       <c r="H32" s="1">
-        <v>47.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="33" spans="1:8">

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -696,25 +696,25 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
       <c r="J4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L4">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M4" s="1">
-        <v>27.1</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -737,25 +737,25 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5">
+        <v>43</v>
+      </c>
+      <c r="I5">
         <v>45</v>
       </c>
-      <c r="I5">
-        <v>50</v>
-      </c>
       <c r="J5">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K5">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="L5">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M5" s="1">
-        <v>42.5</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -848,7 +848,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>13</v>
@@ -875,10 +875,10 @@
         <v>61</v>
       </c>
       <c r="L8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M8" s="1">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -889,7 +889,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -904,7 +904,7 @@
         <v>29</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9">
         <v>54</v>
@@ -916,10 +916,10 @@
         <v>193</v>
       </c>
       <c r="L9">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M9" s="1">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -927,7 +927,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -939,25 +939,25 @@
         <v>33</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H10">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I10">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J10">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K10">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="L10">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M10" s="1">
-        <v>48</v>
+        <v>47.4</v>
       </c>
     </row>
   </sheetData>
@@ -1084,16 +1084,16 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K3">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M3" s="1">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1116,25 +1116,25 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K4">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="L4">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="M4" s="1">
-        <v>36.2</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1157,25 +1157,25 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="K5">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="L5">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="M5" s="1">
-        <v>38.9</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1268,7 +1268,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>14</v>
@@ -1295,10 +1295,10 @@
         <v>60</v>
       </c>
       <c r="L8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M8" s="1">
-        <v>48.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D9">
         <v>17</v>
@@ -1324,7 +1324,7 @@
         <v>32</v>
       </c>
       <c r="H9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I9">
         <v>46</v>
@@ -1336,10 +1336,10 @@
         <v>187</v>
       </c>
       <c r="L9">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M9" s="1">
-        <v>56.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1347,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D10">
         <v>23</v>
@@ -1359,25 +1359,25 @@
         <v>32</v>
       </c>
       <c r="G10">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I10">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="K10">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="L10">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="M10" s="1">
-        <v>46.4</v>
+        <v>43.6</v>
       </c>
     </row>
   </sheetData>
@@ -1504,16 +1504,16 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K3">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M3" s="1">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1536,25 +1536,25 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L4">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M4" s="1">
-        <v>25.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1577,25 +1577,25 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="K5">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="L5">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="M5" s="1">
-        <v>35.6</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1688,7 +1688,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>14</v>
@@ -1715,10 +1715,10 @@
         <v>60</v>
       </c>
       <c r="L8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M8" s="1">
-        <v>48.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1729,7 +1729,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D9">
         <v>17</v>
@@ -1744,7 +1744,7 @@
         <v>32</v>
       </c>
       <c r="H9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I9">
         <v>46</v>
@@ -1756,10 +1756,10 @@
         <v>187</v>
       </c>
       <c r="L9">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M9" s="1">
-        <v>56.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1767,7 +1767,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D10">
         <v>23</v>
@@ -1779,25 +1779,25 @@
         <v>32</v>
       </c>
       <c r="G10">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="K10">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="L10">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="M10" s="1">
-        <v>44.5</v>
+        <v>43.4</v>
       </c>
     </row>
   </sheetData>
@@ -2257,16 +2257,16 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L12" s="1">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2324,25 +2324,25 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L14" s="1">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2371,16 +2371,16 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2479,22 +2479,22 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>3</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L18" s="1">
-        <v>39.3</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2517,22 +2517,22 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K19">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L19" s="1">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3072,7 +3072,7 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -3099,10 +3099,10 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L34" s="1">
-        <v>41.7</v>
+        <v>46.2</v>
       </c>
     </row>
   </sheetData>
@@ -3415,19 +3415,19 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1">
         <v>37.5</v>
       </c>
       <c r="G12" s="1">
-        <v>71.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>71.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3467,19 +3467,19 @@
         <v>20</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1">
         <v>66.7</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H14" s="1">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3490,22 +3490,22 @@
         <v>38</v>
       </c>
       <c r="C15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G15" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3568,22 +3568,22 @@
         <v>28</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D18">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1">
-        <v>60.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G18" s="1">
-        <v>60.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>60.7</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3594,22 +3594,22 @@
         <v>36</v>
       </c>
       <c r="C19">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1">
-        <v>63.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G19" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="H19" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3981,7 +3981,7 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -3993,13 +3993,13 @@
         <v>7</v>
       </c>
       <c r="F34" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="G34" s="1">
-        <v>58.3</v>
+        <v>53.8</v>
       </c>
       <c r="H34" s="1">
-        <v>58.3</v>
+        <v>53.8</v>
       </c>
     </row>
   </sheetData>

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -620,10 +620,10 @@
         <v>27</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K2">
         <v>66</v>
@@ -743,10 +743,10 @@
         <v>43</v>
       </c>
       <c r="I5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J5">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K5">
         <v>354</v>
@@ -945,10 +945,10 @@
         <v>80</v>
       </c>
       <c r="I10">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J10">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K10">
         <v>547</v>
@@ -1125,16 +1125,16 @@
         <v>12</v>
       </c>
       <c r="J4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K4">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M4" s="1">
-        <v>21.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1166,16 +1166,16 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K5">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L5">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M5" s="1">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1248,16 +1248,16 @@
         <v>11</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" s="1">
-        <v>37.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1286,19 +1286,19 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J8">
         <v>29</v>
       </c>
       <c r="K8">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L8">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M8" s="1">
-        <v>48.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1327,19 +1327,19 @@
         <v>34</v>
       </c>
       <c r="I9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J9">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K9">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L9">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M9" s="1">
-        <v>57</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1365,19 +1365,19 @@
         <v>68</v>
       </c>
       <c r="I10">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K10">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="L10">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="M10" s="1">
-        <v>43.6</v>
+        <v>43.2</v>
       </c>
     </row>
   </sheetData>
@@ -1445,34 +1445,34 @@
         <v>194</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2">
         <v>6</v>
       </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>12</v>
-      </c>
-      <c r="H2">
-        <v>21</v>
-      </c>
       <c r="I2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="M2" s="1">
-        <v>56.2</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1489,31 +1489,31 @@
         <v>0</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
         <v>15</v>
       </c>
-      <c r="J3">
-        <v>26</v>
-      </c>
       <c r="K3">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="L3">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="M3" s="1">
-        <v>25.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1527,34 +1527,34 @@
         <v>188</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
       <c r="J4">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="L4">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="M4" s="1">
-        <v>20.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1568,34 +1568,34 @@
         <v>604</v>
       </c>
       <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
         <v>6</v>
       </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
       <c r="F5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I5">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="K5">
-        <v>401</v>
+        <v>483</v>
       </c>
       <c r="L5">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="M5" s="1">
-        <v>33.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1609,34 +1609,34 @@
         <v>170</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
         <v>12</v>
       </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
       <c r="G6">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>21</v>
       </c>
       <c r="J6">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K6">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L6">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="M6" s="1">
-        <v>80</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1656,28 +1656,28 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
       <c r="J7">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K7">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="L7">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="M7" s="1">
-        <v>37.2</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1697,28 +1697,28 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K8">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L8">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="M8" s="1">
-        <v>48.7</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1732,34 +1732,34 @@
         <v>435</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H9">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I9">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="J9">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K9">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="L9">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="M9" s="1">
-        <v>57</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1770,34 +1770,34 @@
         <v>1039</v>
       </c>
       <c r="D10">
+        <v>24</v>
+      </c>
+      <c r="E10">
+        <v>25</v>
+      </c>
+      <c r="F10">
+        <v>21</v>
+      </c>
+      <c r="G10">
         <v>23</v>
       </c>
-      <c r="E10">
-        <v>27</v>
-      </c>
-      <c r="F10">
-        <v>32</v>
-      </c>
-      <c r="G10">
-        <v>46</v>
-      </c>
       <c r="H10">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="J10">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="K10">
-        <v>588</v>
+        <v>723</v>
       </c>
       <c r="L10">
-        <v>451</v>
+        <v>316</v>
       </c>
       <c r="M10" s="1">
-        <v>43.4</v>
+        <v>30.4</v>
       </c>
     </row>
   </sheetData>
@@ -1859,34 +1859,34 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L2" s="1">
-        <v>70.40000000000001</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1900,31 +1900,31 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>6</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
       <c r="J3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L3" s="1">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1938,31 +1938,31 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L4" s="1">
-        <v>38.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1973,34 +1973,34 @@
         <v>40</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>30</v>
+      </c>
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="J5">
-        <v>22</v>
-      </c>
-      <c r="K5">
-        <v>18</v>
-      </c>
       <c r="L5" s="1">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2014,31 +2014,31 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
       <c r="J6">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L6" s="1">
-        <v>53.8</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2052,31 +2052,31 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L7" s="1">
-        <v>73.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2099,22 +2099,22 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L8" s="1">
-        <v>23.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>39</v>
+      </c>
+      <c r="K9">
         <v>3</v>
       </c>
-      <c r="J9">
-        <v>34</v>
-      </c>
-      <c r="K9">
-        <v>8</v>
-      </c>
       <c r="L9" s="1">
-        <v>19</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2175,22 +2175,22 @@
         <v>1</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>2</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
+      <c r="J10">
+        <v>31</v>
+      </c>
+      <c r="K10">
         <v>5</v>
       </c>
-      <c r="J10">
-        <v>27</v>
-      </c>
-      <c r="K10">
-        <v>9</v>
-      </c>
       <c r="L10" s="1">
-        <v>25</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2207,28 +2207,28 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L11" s="1">
-        <v>36.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2248,25 +2248,25 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>3</v>
       </c>
       <c r="J12">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L12" s="1">
-        <v>21.9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2286,25 +2286,25 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>3</v>
       </c>
-      <c r="I13">
-        <v>4</v>
-      </c>
       <c r="J13">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L13" s="1">
-        <v>23.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2327,22 +2327,22 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L14" s="1">
-        <v>26.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2371,16 +2371,16 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2397,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2409,16 +2409,16 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L16" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2447,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2467,34 +2467,34 @@
         <v>28</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2520,19 +2520,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2543,34 +2543,34 @@
         <v>36</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>4</v>
       </c>
       <c r="H20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L20" s="1">
-        <v>80.59999999999999</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2581,34 +2581,34 @@
         <v>39</v>
       </c>
       <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
+      <c r="G21">
+        <v>6</v>
+      </c>
+      <c r="H21">
         <v>4</v>
       </c>
-      <c r="F21">
-        <v>6</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-      <c r="H21">
-        <v>5</v>
-      </c>
       <c r="I21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K21">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="L21" s="1">
-        <v>79.5</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2619,34 +2619,34 @@
         <v>39</v>
       </c>
       <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <v>12</v>
+      </c>
+      <c r="J22">
         <v>5</v>
       </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22">
-        <v>6</v>
-      </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-      <c r="H22">
-        <v>4</v>
-      </c>
-      <c r="I22">
-        <v>8</v>
-      </c>
-      <c r="J22">
-        <v>7</v>
-      </c>
       <c r="K22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L22" s="1">
-        <v>82.09999999999999</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2657,25 +2657,25 @@
         <v>37</v>
       </c>
       <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
         <v>5</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>3</v>
       </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>9</v>
-      </c>
       <c r="G23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -2695,34 +2695,34 @@
         <v>19</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
         <v>2</v>
       </c>
-      <c r="G24">
-        <v>3</v>
-      </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24">
         <v>2</v>
       </c>
       <c r="J24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L24" s="1">
-        <v>68.40000000000001</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2745,22 +2745,22 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K25">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L25" s="1">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2774,31 +2774,31 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>2</v>
       </c>
       <c r="I26">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K26">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L26" s="1">
-        <v>43.9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2815,19 +2815,19 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
         <v>2</v>
       </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
       <c r="H27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27">
         <v>16</v>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2862,19 +2862,19 @@
         <v>1</v>
       </c>
       <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>3</v>
       </c>
-      <c r="I28">
-        <v>2</v>
-      </c>
       <c r="J28">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L28" s="1">
-        <v>29.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2897,22 +2897,22 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L29" s="1">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2938,19 +2938,19 @@
         <v>1</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L30" s="1">
-        <v>39.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2970,25 +2970,25 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>3</v>
       </c>
       <c r="I31">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K31">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L31" s="1">
-        <v>54.5</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3011,22 +3011,22 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K32">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L32" s="1">
-        <v>58.8</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -3043,28 +3043,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L33" s="1">
-        <v>46.2</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3087,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34" s="1">
-        <v>46.2</v>
+        <v>38.5</v>
       </c>
     </row>
   </sheetData>
@@ -3158,7 +3158,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1">
         <v>33.3</v>
@@ -3167,7 +3167,7 @@
         <v>29.6</v>
       </c>
       <c r="H2" s="1">
-        <v>29.6</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3184,7 +3184,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1">
         <v>33.3</v>
@@ -3193,7 +3193,7 @@
         <v>33.3</v>
       </c>
       <c r="H3" s="1">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3210,7 +3210,7 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1">
         <v>41.2</v>
@@ -3219,7 +3219,7 @@
         <v>61.8</v>
       </c>
       <c r="H4" s="1">
-        <v>61.8</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3236,7 +3236,7 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F5" s="1">
         <v>42.5</v>
@@ -3245,7 +3245,7 @@
         <v>55</v>
       </c>
       <c r="H5" s="1">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3262,7 +3262,7 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1">
         <v>30.8</v>
@@ -3271,7 +3271,7 @@
         <v>46.2</v>
       </c>
       <c r="H6" s="1">
-        <v>46.2</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3288,7 +3288,7 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1">
         <v>20</v>
@@ -3297,7 +3297,7 @@
         <v>26.7</v>
       </c>
       <c r="H7" s="1">
-        <v>26.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3314,7 +3314,7 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1">
         <v>70</v>
@@ -3323,7 +3323,7 @@
         <v>76.7</v>
       </c>
       <c r="H8" s="1">
-        <v>76.7</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3340,7 +3340,7 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F9" s="1">
         <v>76.2</v>
@@ -3349,7 +3349,7 @@
         <v>81</v>
       </c>
       <c r="H9" s="1">
-        <v>81</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3366,7 +3366,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1">
         <v>66.7</v>
@@ -3375,7 +3375,7 @@
         <v>75</v>
       </c>
       <c r="H10" s="1">
-        <v>75</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3392,7 +3392,7 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1">
         <v>61.4</v>
@@ -3401,7 +3401,7 @@
         <v>63.6</v>
       </c>
       <c r="H11" s="1">
-        <v>63.6</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3418,7 +3418,7 @@
         <v>25</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1">
         <v>37.5</v>
@@ -3427,7 +3427,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>78.09999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3444,7 +3444,7 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F13" s="1">
         <v>73.7</v>
@@ -3453,7 +3453,7 @@
         <v>76.3</v>
       </c>
       <c r="H13" s="1">
-        <v>76.3</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3467,19 +3467,19 @@
         <v>20</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1">
         <v>66.7</v>
       </c>
       <c r="G14" s="1">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="H14" s="1">
-        <v>73.3</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3496,7 +3496,7 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F15" s="1">
         <v>94.7</v>
@@ -3505,7 +3505,7 @@
         <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3522,7 +3522,7 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1">
         <v>80</v>
@@ -3531,7 +3531,7 @@
         <v>76</v>
       </c>
       <c r="H16" s="1">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3548,7 +3548,7 @@
         <v>26</v>
       </c>
       <c r="E17">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1">
         <v>74.2</v>
@@ -3557,7 +3557,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3574,7 +3574,7 @@
         <v>20</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1">
         <v>71.40000000000001</v>
@@ -3583,7 +3583,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>71.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3600,7 +3600,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F19" s="1">
         <v>69.40000000000001</v>
@@ -3609,7 +3609,7 @@
         <v>75</v>
       </c>
       <c r="H19" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3626,7 +3626,7 @@
         <v>7</v>
       </c>
       <c r="E20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1">
         <v>22.2</v>
@@ -3635,7 +3635,7 @@
         <v>19.4</v>
       </c>
       <c r="H20" s="1">
-        <v>19.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1">
         <v>15.4</v>
@@ -3661,7 +3661,7 @@
         <v>20.5</v>
       </c>
       <c r="H21" s="1">
-        <v>20.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3678,7 +3678,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" s="1">
         <v>28.2</v>
@@ -3687,7 +3687,7 @@
         <v>17.9</v>
       </c>
       <c r="H22" s="1">
-        <v>17.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3730,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1">
         <v>36.8</v>
@@ -3739,7 +3739,7 @@
         <v>31.6</v>
       </c>
       <c r="H24" s="1">
-        <v>31.6</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3753,19 +3753,19 @@
         <v>12</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1">
         <v>48</v>
       </c>
       <c r="G25" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H25" s="1">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3782,7 +3782,7 @@
         <v>23</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1">
         <v>63.4</v>
@@ -3791,7 +3791,7 @@
         <v>56.1</v>
       </c>
       <c r="H26" s="1">
-        <v>56.1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3834,7 +3834,7 @@
         <v>19</v>
       </c>
       <c r="E28">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1">
         <v>66.7</v>
@@ -3843,7 +3843,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>70.40000000000001</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3860,7 +3860,7 @@
         <v>26</v>
       </c>
       <c r="E29">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F29" s="1">
         <v>86.7</v>
@@ -3869,7 +3869,7 @@
         <v>86.7</v>
       </c>
       <c r="H29" s="1">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3886,7 +3886,7 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1">
         <v>64.3</v>
@@ -3895,7 +3895,7 @@
         <v>60.7</v>
       </c>
       <c r="H30" s="1">
-        <v>60.7</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3912,7 +3912,7 @@
         <v>15</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1">
         <v>42.4</v>
@@ -3921,7 +3921,7 @@
         <v>45.5</v>
       </c>
       <c r="H31" s="1">
-        <v>45.5</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3938,7 +3938,7 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F32" s="1">
         <v>47.1</v>
@@ -3947,7 +3947,7 @@
         <v>41.2</v>
       </c>
       <c r="H32" s="1">
-        <v>41.2</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3961,19 +3961,19 @@
         <v>19</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1">
         <v>73.09999999999999</v>
       </c>
       <c r="G33" s="1">
-        <v>53.8</v>
+        <v>57.7</v>
       </c>
       <c r="H33" s="1">
-        <v>53.8</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3990,7 +3990,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1">
         <v>15.4</v>
@@ -3999,7 +3999,7 @@
         <v>53.8</v>
       </c>
       <c r="H34" s="1">
-        <v>53.8</v>
+        <v>61.5</v>
       </c>
     </row>
   </sheetData>

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -863,10 +863,10 @@
         <v>3</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8">
         <v>30</v>
@@ -904,10 +904,10 @@
         <v>29</v>
       </c>
       <c r="H9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J9">
         <v>84</v>
@@ -942,10 +942,10 @@
         <v>50</v>
       </c>
       <c r="H10">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I10">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10">
         <v>201</v>
@@ -1283,10 +1283,10 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8">
         <v>29</v>
@@ -1324,10 +1324,10 @@
         <v>32</v>
       </c>
       <c r="H9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J9">
         <v>78</v>
@@ -1362,10 +1362,10 @@
         <v>46</v>
       </c>
       <c r="H10">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
         <v>166</v>
@@ -1609,25 +1609,25 @@
         <v>170</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K6">
         <v>43</v>
@@ -1694,31 +1694,31 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
       <c r="J8">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="L8">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="M8" s="1">
-        <v>32.5</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1732,34 +1732,34 @@
         <v>435</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H9">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I9">
         <v>31</v>
       </c>
       <c r="J9">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K9">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="L9">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="M9" s="1">
-        <v>44.8</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1770,34 +1770,34 @@
         <v>1039</v>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10">
+        <v>26</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10">
         <v>25</v>
       </c>
-      <c r="F10">
-        <v>21</v>
-      </c>
-      <c r="G10">
-        <v>23</v>
-      </c>
       <c r="H10">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I10">
         <v>49</v>
       </c>
       <c r="J10">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K10">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="L10">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="M10" s="1">
-        <v>30.4</v>
+        <v>29.2</v>
       </c>
     </row>
   </sheetData>
@@ -2543,25 +2543,25 @@
         <v>36</v>
       </c>
       <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
         <v>5</v>
       </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>4</v>
-      </c>
-      <c r="H20">
-        <v>4</v>
-      </c>
       <c r="I20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2660,31 +2660,31 @@
         <v>4</v>
       </c>
       <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="E23">
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
         <v>5</v>
-      </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-      <c r="H23">
-        <v>3</v>
       </c>
       <c r="I23">
         <v>7</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L23" s="1">
-        <v>83.8</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2707,22 +2707,22 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L24" s="1">
-        <v>57.9</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2926,31 +2926,31 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L30" s="1">
-        <v>35.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2976,19 +2976,19 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L31" s="1">
-        <v>30.3</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3055,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K33">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L33" s="1">
-        <v>34.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3090,19 +3090,19 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L34" s="1">
-        <v>38.5</v>
+        <v>30.8</v>
       </c>
     </row>
   </sheetData>
@@ -3704,7 +3704,7 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1">
         <v>5.4</v>
@@ -3713,7 +3713,7 @@
         <v>16.2</v>
       </c>
       <c r="H23" s="1">
-        <v>16.2</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3730,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1">
         <v>36.8</v>
@@ -3739,7 +3739,7 @@
         <v>31.6</v>
       </c>
       <c r="H24" s="1">
-        <v>42.1</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3886,7 +3886,7 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F30" s="1">
         <v>64.3</v>
@@ -3895,7 +3895,7 @@
         <v>60.7</v>
       </c>
       <c r="H30" s="1">
-        <v>64.3</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3912,7 +3912,7 @@
         <v>15</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1">
         <v>42.4</v>
@@ -3921,7 +3921,7 @@
         <v>45.5</v>
       </c>
       <c r="H31" s="1">
-        <v>69.7</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3964,7 +3964,7 @@
         <v>15</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F33" s="1">
         <v>73.09999999999999</v>
@@ -3973,7 +3973,7 @@
         <v>57.7</v>
       </c>
       <c r="H33" s="1">
-        <v>65.40000000000001</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3990,7 +3990,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1">
         <v>15.4</v>
@@ -3999,7 +3999,7 @@
         <v>53.8</v>
       </c>
       <c r="H34" s="1">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
     </row>
   </sheetData>

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -828,16 +828,16 @@
         <v>18</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L7">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M7" s="1">
-        <v>33.8</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -910,16 +910,16 @@
         <v>55</v>
       </c>
       <c r="J9">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K9">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L9">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M9" s="1">
-        <v>55.6</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -948,16 +948,16 @@
         <v>99</v>
       </c>
       <c r="J10">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K10">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L10">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="M10" s="1">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
   </sheetData>
@@ -1463,16 +1463,16 @@
         <v>11</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1">
-        <v>39.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1542,19 +1542,19 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M4" s="1">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1583,19 +1583,19 @@
         <v>13</v>
       </c>
       <c r="I5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L5">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M5" s="1">
-        <v>20</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1615,28 +1615,28 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>13</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K6">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L6">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M6" s="1">
-        <v>74.7</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1662,22 +1662,22 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M7" s="1">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1703,22 +1703,22 @@
         <v>0</v>
       </c>
       <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>5</v>
       </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
       <c r="J8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K8">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M8" s="1">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1738,28 +1738,28 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>14</v>
       </c>
       <c r="H9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>31</v>
       </c>
       <c r="J9">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K9">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="L9">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M9" s="1">
-        <v>41.8</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1776,28 +1776,28 @@
         <v>26</v>
       </c>
       <c r="F10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>25</v>
       </c>
       <c r="H10">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I10">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J10">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="K10">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="L10">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="M10" s="1">
-        <v>29.2</v>
+        <v>28.3</v>
       </c>
     </row>
   </sheetData>
@@ -2029,16 +2029,16 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1">
-        <v>25.6</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2406,10 +2406,10 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>22</v>
@@ -2447,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2552,25 +2552,25 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L20" s="1">
-        <v>75</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2625,28 +2625,28 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
         <v>3</v>
       </c>
-      <c r="G22">
-        <v>4</v>
-      </c>
       <c r="H22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L22" s="1">
-        <v>87.2</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2783,22 +2783,22 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
         <v>2</v>
       </c>
-      <c r="I26">
-        <v>3</v>
-      </c>
       <c r="J26">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L26" s="1">
-        <v>22</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2859,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>3</v>
@@ -2935,22 +2935,22 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>2</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L30" s="1">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -3011,10 +3011,10 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -3262,7 +3262,7 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1">
         <v>30.8</v>
@@ -3271,7 +3271,7 @@
         <v>46.2</v>
       </c>
       <c r="H6" s="1">
-        <v>74.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3548,7 +3548,7 @@
         <v>26</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17" s="1">
         <v>74.2</v>
@@ -3557,7 +3557,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3626,7 +3626,7 @@
         <v>7</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1">
         <v>22.2</v>
@@ -3635,7 +3635,7 @@
         <v>19.4</v>
       </c>
       <c r="H20" s="1">
-        <v>25</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3678,7 +3678,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22" s="1">
         <v>28.2</v>
@@ -3687,7 +3687,7 @@
         <v>17.9</v>
       </c>
       <c r="H22" s="1">
-        <v>12.8</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3782,7 +3782,7 @@
         <v>23</v>
       </c>
       <c r="E26">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" s="1">
         <v>63.4</v>
@@ -3791,7 +3791,7 @@
         <v>56.1</v>
       </c>
       <c r="H26" s="1">
-        <v>78</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3828,7 +3828,7 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28">
         <v>19</v>
@@ -3837,7 +3837,7 @@
         <v>22</v>
       </c>
       <c r="F28" s="1">
-        <v>66.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G28" s="1">
         <v>70.40000000000001</v>
@@ -3886,7 +3886,7 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F30" s="1">
         <v>64.3</v>
@@ -3895,7 +3895,7 @@
         <v>60.7</v>
       </c>
       <c r="H30" s="1">
-        <v>71.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:8">

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -1454,10 +1454,10 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>11</v>
@@ -1577,10 +1577,10 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5">
         <v>19</v>
@@ -1612,31 +1612,31 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>16</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K6">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="L6">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="M6" s="1">
-        <v>72.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1662,22 +1662,22 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>5</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L7">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M7" s="1">
-        <v>19.6</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1700,25 +1700,25 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>3</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M8" s="1">
-        <v>19.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1735,31 +1735,31 @@
         <v>17</v>
       </c>
       <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+      <c r="H9">
         <v>20</v>
       </c>
-      <c r="F9">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>14</v>
-      </c>
-      <c r="H9">
-        <v>21</v>
-      </c>
       <c r="I9">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K9">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="L9">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="M9" s="1">
-        <v>40.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1773,31 +1773,31 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H10">
         <v>34</v>
       </c>
       <c r="I10">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J10">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K10">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="L10">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="M10" s="1">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
     </row>
   </sheetData>
@@ -1906,10 +1906,10 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -2584,31 +2584,31 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K21">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L21" s="1">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2628,25 +2628,25 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
         <v>3</v>
       </c>
-      <c r="H22">
-        <v>6</v>
-      </c>
       <c r="I22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K22">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L22" s="1">
-        <v>74.40000000000001</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2660,31 +2660,31 @@
         <v>4</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L23" s="1">
-        <v>81.09999999999999</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2710,19 +2710,19 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>4</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L24" s="1">
-        <v>63.2</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2821,22 +2821,22 @@
         <v>1</v>
       </c>
       <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
         <v>2</v>
       </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>4</v>
-      </c>
       <c r="J27">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L27" s="1">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2903,16 +2903,16 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2970,25 +2970,25 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L31" s="1">
-        <v>21.2</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21" s="1">
         <v>15.4</v>
@@ -3661,7 +3661,7 @@
         <v>20.5</v>
       </c>
       <c r="H21" s="1">
-        <v>38.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3678,7 +3678,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1">
         <v>28.2</v>
@@ -3687,7 +3687,7 @@
         <v>17.9</v>
       </c>
       <c r="H22" s="1">
-        <v>25.6</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3704,7 +3704,7 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1">
         <v>5.4</v>
@@ -3713,7 +3713,7 @@
         <v>16.2</v>
       </c>
       <c r="H23" s="1">
-        <v>18.9</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3730,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24" s="1">
         <v>36.8</v>
@@ -3739,7 +3739,7 @@
         <v>31.6</v>
       </c>
       <c r="H24" s="1">
-        <v>36.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F27" s="1">
         <v>64</v>
@@ -3817,7 +3817,7 @@
         <v>64</v>
       </c>
       <c r="H27" s="1">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3860,7 +3860,7 @@
         <v>26</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1">
         <v>86.7</v>
@@ -3869,7 +3869,7 @@
         <v>86.7</v>
       </c>
       <c r="H29" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3912,7 +3912,7 @@
         <v>15</v>
       </c>
       <c r="E31">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1">
         <v>42.4</v>
@@ -3921,7 +3921,7 @@
         <v>45.5</v>
       </c>
       <c r="H31" s="1">
-        <v>78.8</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="32" spans="1:8">

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -605,19 +605,19 @@
         <v>194</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I2">
         <v>23</v>
@@ -728,19 +728,19 @@
         <v>604</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5">
         <v>44</v>
@@ -769,22 +769,22 @@
         <v>170</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
         <v>18</v>
       </c>
-      <c r="G6">
-        <v>21</v>
-      </c>
       <c r="H6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <v>37</v>
@@ -892,22 +892,22 @@
         <v>435</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9">
         <v>83</v>
@@ -933,19 +933,19 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10">
         <v>33</v>
       </c>
       <c r="G10">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H10">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I10">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J10">
         <v>200</v>
@@ -1025,16 +1025,16 @@
         <v>194</v>
       </c>
       <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
       <c r="F2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>21</v>
@@ -1148,16 +1148,16 @@
         <v>604</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5">
         <v>34</v>
@@ -1189,13 +1189,13 @@
         <v>170</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>27</v>
@@ -1312,13 +1312,13 @@
         <v>435</v>
       </c>
       <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
         <v>17</v>
       </c>
-      <c r="E9">
-        <v>18</v>
-      </c>
       <c r="F9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9">
         <v>32</v>
@@ -1350,16 +1350,16 @@
         <v>1039</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <v>32</v>
       </c>
       <c r="G10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H10">
         <v>67</v>
@@ -1445,16 +1445,16 @@
         <v>194</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -1568,16 +1568,16 @@
         <v>604</v>
       </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
       <c r="G5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -1609,34 +1609,34 @@
         <v>170</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
         <v>16</v>
       </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
       <c r="J6">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K6">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="L6">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="M6" s="1">
-        <v>64.09999999999999</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1732,34 +1732,34 @@
         <v>435</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
         <v>14</v>
       </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>12</v>
-      </c>
       <c r="H9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J9">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K9">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="L9">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="M9" s="1">
-        <v>36.6</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1770,34 +1770,34 @@
         <v>1039</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>20</v>
       </c>
       <c r="F10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>22</v>
       </c>
       <c r="H10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I10">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J10">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="K10">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="L10">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="M10" s="1">
-        <v>26.8</v>
+        <v>28.5</v>
       </c>
     </row>
   </sheetData>
@@ -1859,16 +1859,16 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1897,7 +1897,7 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1973,16 +1973,16 @@
         <v>40</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2049,10 +2049,10 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L21" s="1">
-        <v>53.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2622,7 +2622,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2657,19 +2657,19 @@
         <v>37</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>3</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1">
         <v>15.4</v>
@@ -3661,7 +3661,7 @@
         <v>20.5</v>
       </c>
       <c r="H21" s="1">
-        <v>46.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">

--- a/Totales Generales20231.xlsx
+++ b/Totales Generales20231.xlsx
@@ -1542,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>176</v>
@@ -1583,10 +1583,10 @@
         <v>14</v>
       </c>
       <c r="I5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5">
         <v>485</v>
@@ -1621,22 +1621,22 @@
         <v>12</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M6" s="1">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1709,16 +1709,16 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" s="1">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1744,22 +1744,22 @@
         <v>14</v>
       </c>
       <c r="H9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K9">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L9">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M9" s="1">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1782,22 +1782,22 @@
         <v>22</v>
       </c>
       <c r="H10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I10">
         <v>46</v>
       </c>
       <c r="J10">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K10">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L10">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M10" s="1">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
     </row>
   </sheetData>
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>22</v>
@@ -2555,10 +2555,10 @@
         <v>2</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -2637,16 +2637,16 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L22" s="1">
-        <v>56.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3055,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3678,7 +3678,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1">
         <v>28.2</v>
@@ -3687,7 +3687,7 @@
         <v>17.9</v>
       </c>
       <c r="H22" s="1">
-        <v>43.6</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3964,7 +3964,7 @@
         <v>15</v>
       </c>
       <c r="E33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F33" s="1">
         <v>73.09999999999999</v>
@@ -3973,7 +3973,7 @@
         <v>57.7</v>
       </c>
       <c r="H33" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="34" spans="1:8">
